--- a/03_Prompting/outputs/GPT/RESULT_f-droid_gpt-4o_fewshot_cot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_f-droid_gpt-4o_fewshot_cot.xlsx
@@ -2176,7 +2176,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -5136,7 +5136,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -6411,7 +6411,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9012,7 +9012,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -10168,7 +10168,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10542,7 +10542,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -10916,7 +10916,7 @@
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -11103,7 +11103,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -11188,7 +11188,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -12871,7 +12871,7 @@
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -14554,7 +14554,7 @@
       </c>
       <c r="C831" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15353,7 +15353,7 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15693,7 +15693,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -15812,7 +15812,7 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16526,7 +16526,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -16951,7 +16951,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17155,7 +17155,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -17988,7 +17988,7 @@
       </c>
       <c r="C1033" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18192,7 +18192,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18328,7 +18328,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18600,7 +18600,7 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -18651,7 +18651,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -18872,7 +18872,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>FEATURE &amp; UI BUGS</t>
+          <t>CRASHES</t>
         </is>
       </c>
     </row>
@@ -20130,7 +20130,7 @@
       </c>
       <c r="C1159" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -20742,7 +20742,7 @@
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -26972,7 +26972,7 @@
       </c>
       <c r="C1561" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -30882,7 +30882,7 @@
       </c>
       <c r="C1791" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -48443,7 +48443,7 @@
       </c>
       <c r="C2824" t="inlineStr">
         <is>
-          <t>CRASHES</t>
+          <t>FEATURE &amp; UI BUGS</t>
         </is>
       </c>
     </row>
@@ -48786,7 +48786,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6448433650123196</v>
+        <v>0.6381555790214714</v>
       </c>
     </row>
     <row r="3">
@@ -48796,7 +48796,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5292075619943907</v>
+        <v>0.5146811322159357</v>
       </c>
     </row>
     <row r="4">
@@ -48806,7 +48806,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.5650973673344722</v>
+        <v>0.5523352377665421</v>
       </c>
     </row>
     <row r="5">
@@ -48816,7 +48816,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7692192864606657</v>
+        <v>0.7691346880123801</v>
       </c>
     </row>
     <row r="6">
@@ -48826,7 +48826,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5823901388675982</v>
+        <v>0.5741539167484739</v>
       </c>
     </row>
     <row r="7">
@@ -48836,7 +48836,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>821.3999597469992</v>
+        <v>1408.65118842799</v>
       </c>
     </row>
     <row r="8">
@@ -48846,7 +48846,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2891235338778597</v>
+        <v>0.4958293517873952</v>
       </c>
     </row>
   </sheetData>
